--- a/JsonConverter/ExcelFiles/Character.xlsx
+++ b/JsonConverter/ExcelFiles/Character.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fileVersion appName="HCell" lastEdited="12.0" lowestEdited="12.0" rupBuild="0.535"/>
+  <x:fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.12458"/>
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\0_NRUnityProjects\UnityBasic_6\JsonConverter\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BootCamp\2D_Evaulation\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="4294939940" windowHeight="16840"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="18852" windowHeight="6744"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId4"/>
@@ -21,88 +21,88 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="28">
   <x:si>
+    <x:t>셀리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>빅토르</x:t>
+  </x:si>
+  <x:si>
     <x:t>Id</x:t>
   </x:si>
   <x:si>
-    <x:t>빅토르</x:t>
-  </x:si>
-  <x:si>
-    <x:t>헬레나</x:t>
-  </x:si>
-  <x:si>
     <x:t>스킬</x:t>
   </x:si>
   <x:si>
     <x:t>다니엘</x:t>
   </x:si>
   <x:si>
-    <x:t>skill_fireball_01,skill_normalSword_01</x:t>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>character_daniel_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 별로 무기가 고정인 경우용</x:t>
   </x:si>
   <x:si>
     <x:t>소환 마법을 사용할 수 있는 캐릭터</x:t>
   </x:si>
   <x:si>
+    <x:t>character_selly_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>character_victor_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Weapon_CoffeeCup_1</x:t>
+  </x:si>
+  <x:si>
     <x:t>Weapon_Braclet_1</x:t>
   </x:si>
   <x:si>
-    <x:t>캐릭터 별로 무기가 고정인 경우용</x:t>
-  </x:si>
-  <x:si>
-    <x:t>character_daniel_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>character_victor_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Weapon_CoffeeCup_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>모든 마법을 사용할 수 있는 캐릭터</x:t>
+    <x:t>Weapon_Sword_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BasicCostumeId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_sword_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UseWeaponId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillList</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
   </x:si>
   <x:si>
     <x:t>캐릭터 고유 ID</x:t>
   </x:si>
   <x:si>
-    <x:t>SkillList</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UseWeaponId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
     <x:t>잉여로운 버프 캐릭터</x:t>
   </x:si>
   <x:si>
     <x:t>Costume_03</x:t>
   </x:si>
   <x:si>
-    <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BasicCostumeId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Weapon_Sword_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>character_hellena_01</x:t>
+    <x:t>퐁당퐁당 왕국의 공주로써 백성들을 위해&lt;nl&gt;식량을 구하러 모험을 떠나는 캐릭터</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_normalSword_01</x:t>
   </x:si>
   <x:si>
     <x:t>skill_rest_coffee_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_normalSword_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -203,16 +203,16 @@
   <x:borders count="3">
     <x:border>
       <x:left>
-        <x:color rgb="ff000000"/>
+        <x:color auto="1"/>
       </x:left>
       <x:right>
-        <x:color rgb="ff000000"/>
+        <x:color auto="1"/>
       </x:right>
       <x:top>
         <x:color auto="1"/>
       </x:top>
       <x:bottom>
-        <x:color rgb="ff000000"/>
+        <x:color auto="1"/>
       </x:bottom>
     </x:border>
     <x:border>
@@ -251,21 +251,21 @@
   </x:cellStyleXfs>
   <x:cellXfs count="17">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <x:alignment horizontal="general" vertical="bottom"/>
+      <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -274,28 +274,28 @@
     <x:xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -305,8 +305,406 @@
   <x:cellStyles count="1">
     <x:cellStyle name="표준" xfId="0" builtinId="0"/>
   </x:cellStyles>
-  <x:dxfs count="0"/>
-  <x:tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <x:dxfs count="12">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ffd7dff4"/>
+              <x:bgColor rgb="ffd7dff4"/>
+            </x:patternFill>
+          </x:fill>
+          <x:border>
+            <x:left style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:left>
+            <x:right style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:right>
+            <x:top style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:top>
+            <x:bottom style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:bottom>
+            <x:vertical style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:vertical>
+            <x:horizontal style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:horizontal>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ff000000"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ffd7dff4"/>
+              <x:bgColor rgb="ffd7dff4"/>
+            </x:patternFill>
+          </x:fill>
+          <x:border>
+            <x:left style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:left>
+            <x:right style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:right>
+            <x:top style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:top>
+            <x:bottom style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:bottom>
+            <x:vertical style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:vertical>
+            <x:horizontal style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:horizontal>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <x:dxf/>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:fgColor rgb="ffaebfea"/>
+          <x:bgColor rgb="ffaebfea"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ffffffff"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ff6182d6"/>
+              <x:bgColor rgb="ff6182d6"/>
+            </x:patternFill>
+          </x:fill>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ffffffff"/>
+            <x:b val="1"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ff6182d6"/>
+              <x:bgColor rgb="ff6182d6"/>
+            </x:patternFill>
+          </x:fill>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ffffffff"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ff6182d6"/>
+              <x:bgColor rgb="ff6182d6"/>
+            </x:patternFill>
+          </x:fill>
+          <x:border>
+            <x:top style="thick">
+              <x:color rgb="ffffffff"/>
+            </x:top>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ffffffff"/>
+            <x:b val="1"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ff6182d6"/>
+              <x:bgColor rgb="ff6182d6"/>
+            </x:patternFill>
+          </x:fill>
+          <x:border>
+            <x:top style="thick">
+              <x:color rgb="ffffffff"/>
+            </x:top>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ffffffff"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ff6182d6"/>
+              <x:bgColor rgb="ff6182d6"/>
+            </x:patternFill>
+          </x:fill>
+          <x:border>
+            <x:bottom style="thick">
+              <x:color rgb="ffffffff"/>
+            </x:bottom>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ffffffff"/>
+            <x:b val="1"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ff6182d6"/>
+              <x:bgColor rgb="ff6182d6"/>
+            </x:patternFill>
+          </x:fill>
+          <x:border>
+            <x:bottom style="thick">
+              <x:color rgb="ffffffff"/>
+            </x:bottom>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:border>
+            <x:left>
+              <x:color auto="1"/>
+            </x:left>
+            <x:right>
+              <x:color auto="1"/>
+            </x:right>
+            <x:top style="medium">
+              <x:color rgb="ff6182d6"/>
+            </x:top>
+            <x:bottom style="medium">
+              <x:color rgb="ff6182d6"/>
+            </x:bottom>
+            <x:vertical>
+              <x:color auto="1"/>
+            </x:vertical>
+            <x:horizontal>
+              <x:color auto="1"/>
+            </x:horizontal>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ff000000"/>
+          </x:font>
+          <x:border>
+            <x:left>
+              <x:color auto="1"/>
+            </x:left>
+            <x:right>
+              <x:color auto="1"/>
+            </x:right>
+            <x:top style="medium">
+              <x:color rgb="ff6182d6"/>
+            </x:top>
+            <x:bottom style="medium">
+              <x:color rgb="ff6182d6"/>
+            </x:bottom>
+            <x:vertical>
+              <x:color auto="1"/>
+            </x:vertical>
+            <x:horizontal>
+              <x:color auto="1"/>
+            </x:horizontal>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:fgColor rgb="ff94a5df"/>
+          <x:bgColor rgb="ff94a5df"/>
+        </x:patternFill>
+      </x:fill>
+      <x:border>
+        <x:top style="thin">
+          <x:color rgb="ff6182d6"/>
+        </x:top>
+        <x:bottom style="thin">
+          <x:color rgb="ff6182d6"/>
+        </x:bottom>
+      </x:border>
+    </x:dxf>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:fgColor rgb="ff6182d6"/>
+          <x:bgColor rgb="ff6182d6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:b val="1"/>
+          </x:font>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:border>
+            <x:top style="thin">
+              <x:color rgb="ff6182d6"/>
+            </x:top>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:b val="1"/>
+          </x:font>
+          <x:border>
+            <x:top style="thin">
+              <x:color rgb="ff6182d6"/>
+            </x:top>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:border>
+            <x:bottom style="medium">
+              <x:color rgb="ff6182d6"/>
+            </x:bottom>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:b val="1"/>
+          </x:font>
+          <x:border>
+            <x:bottom style="medium">
+              <x:color rgb="ff6182d6"/>
+            </x:bottom>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+  </x:dxfs>
+  <x:tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <x:tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="1" count="9">
+      <x:tableStyleElement type="wholeTable" size="1" dxfId="0"/>
+      <x:tableStyleElement type="headerRow" size="1" dxfId="5"/>
+      <x:tableStyleElement type="totalRow" size="1" dxfId="4"/>
+      <x:tableStyleElement type="firstColumn" size="1" dxfId="3"/>
+      <x:tableStyleElement type="lastColumn" size="1" dxfId="3"/>
+      <x:tableStyleElement type="firstRowStripe" size="1" dxfId="2"/>
+      <x:tableStyleElement type="secondRowStripe" size="1" dxfId="1"/>
+      <x:tableStyleElement type="firstColumnStripe" size="1" dxfId="2"/>
+      <x:tableStyleElement type="secondColumnStripe" size="1" dxfId="1"/>
+    </x:tableStyle>
+    <x:tableStyle name="Light Style 1 - Accent 1" pivot="1" table="0" count="8">
+      <x:tableStyleElement type="wholeTable" size="1" dxfId="6"/>
+      <x:tableStyleElement type="headerRow" size="1" dxfId="11"/>
+      <x:tableStyleElement type="totalRow" size="1" dxfId="10"/>
+      <x:tableStyleElement type="firstColumn" size="1" dxfId="9"/>
+      <x:tableStyleElement type="lastColumn" size="1" dxfId="9"/>
+      <x:tableStyleElement type="firstRowStripe" size="1" dxfId="7"/>
+      <x:tableStyleElement type="secondRowStripe" size="1" dxfId="1"/>
+      <x:tableStyleElement type="firstColumnStripe" size="1" dxfId="8"/>
+    </x:tableStyle>
+  </x:tableStyles>
 </x:styleSheet>
 </file>
 
@@ -506,16 +904,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetPr codeName="Sheet1">
-    <x:outlinePr applyStyles="0" summaryBelow="0" summaryRight="1" showOutlineSymbols="1"/>
-  </x:sheetPr>
+  <x:sheetPr codeName="Sheet1"/>
   <x:dimension ref="A1:O35"/>
   <x:sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15" customHeight="1"/>
   <x:cols>
     <x:col min="1" max="1" width="19.453125" style="3" customWidth="1"/>
     <x:col min="2" max="2" width="19.54296875" style="3" customWidth="1"/>
-    <x:col min="3" max="3" width="50.7265625" style="3" customWidth="1"/>
-    <x:col min="4" max="4" width="20.26953125" style="3" customWidth="1"/>
+    <x:col min="3" max="3" width="72" style="3" customWidth="1"/>
+    <x:col min="4" max="4" width="40.22265625" style="3" customWidth="1"/>
     <x:col min="5" max="5" width="30.54296875" style="3" customWidth="1"/>
     <x:col min="6" max="6" width="26.54296875" style="3" customWidth="1"/>
     <x:col min="7" max="16384" width="12.54296875" style="3"/>
@@ -523,77 +919,77 @@
   <x:sheetData>
     <x:row r="1" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D1" s="2" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="E1" s="2" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:6" ht="13.19999999999999928946">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:6" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:6" s="13" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="12" t="s">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B3" s="12" t="s">
-        <x:v>25</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C3" s="12" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D3" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E3" s="14" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="F3" s="15" t="s">
         <x:v>16</x:v>
-      </x:c>
-      <x:c r="D3" s="14" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="E3" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="F3" s="15" t="s">
-        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A4" s="4" t="s">
-        <x:v>22</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B4" s="4" t="s">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C4" s="4" t="s">
-        <x:v>12</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D4" s="5" t="s">
-        <x:v>5</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E4" s="5" t="s">
-        <x:v>7</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F4" s="16" t="s">
-        <x:v>18</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G4" s="5"/>
       <x:c r="H4" s="5"/>
@@ -607,19 +1003,19 @@
     </x:row>
     <x:row r="5" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A5" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B5" s="6" t="s">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C5" s="6" t="s">
-        <x:v>6</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D5" s="5" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E5" s="5" t="s">
-        <x:v>21</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F5" s="5"/>
       <x:c r="G5" s="5"/>
@@ -634,19 +1030,19 @@
     </x:row>
     <x:row r="6" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A6" s="6" t="s">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B6" s="6" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C6" s="6" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D6" s="5" t="s">
-        <x:v>23</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E6" s="5" t="s">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F6" s="5"/>
       <x:c r="G6" s="5"/>
@@ -1884,7 +2280,7 @@
     <x:row r="999" ht="15.75" customHeight="1"/>
     <x:row r="1000" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:pageMargins left="0.69999998807907104492" right="0.69999998807907104492" top="0.75" bottom="0.75" header="0.30000001192092895508" footer="0.30000001192092895508"/>
+  <x:pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="600" verticalDpi="600" copies="1"/>
 </x:worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/Character.xlsx
+++ b/JsonConverter/ExcelFiles/Character.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="28">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="30">
   <x:si>
     <x:t>셀리</x:t>
   </x:si>
@@ -27,76 +27,82 @@
     <x:t>빅토르</x:t>
   </x:si>
   <x:si>
+    <x:t>스킬</x:t>
+  </x:si>
+  <x:si>
+    <x:t>다니엘</x:t>
+  </x:si>
+  <x:si>
     <x:t>Id</x:t>
   </x:si>
   <x:si>
-    <x:t>스킬</x:t>
-  </x:si>
-  <x:si>
-    <x:t>다니엘</x:t>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>퐁당퐁당 왕국의 공주로써 백성들을 위해&lt;nl&gt;식량을 구하러 모험을 떠나는 캐릭터</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillList</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UseWeaponId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>잉여로운 버프 캐릭터</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Costume_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
   </x:si>
   <x:si>
     <x:t>string</x:t>
   </x:si>
   <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
+    <x:t>캐릭터 별로 무기가 고정인 경우용</x:t>
+  </x:si>
+  <x:si>
+    <x:t>character_victor_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Weapon_CoffeeCup_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>character_selly_01</x:t>
   </x:si>
   <x:si>
     <x:t>character_daniel_01</x:t>
   </x:si>
   <x:si>
-    <x:t>캐릭터 별로 무기가 고정인 경우용</x:t>
+    <x:t>Weapon_Braclet_1</x:t>
   </x:si>
   <x:si>
     <x:t>소환 마법을 사용할 수 있는 캐릭터</x:t>
   </x:si>
   <x:si>
-    <x:t>character_selly_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>character_victor_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Weapon_CoffeeCup_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Weapon_Braclet_1</x:t>
+    <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_sword_01</x:t>
   </x:si>
   <x:si>
     <x:t>Weapon_Sword_1</x:t>
   </x:si>
   <x:si>
     <x:t>BasicCostumeId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_sword_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UseWeaponId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillList</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>잉여로운 버프 캐릭터</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Costume_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>퐁당퐁당 왕국의 공주로써 백성들을 위해&lt;nl&gt;식량을 구하러 모험을 떠나는 캐릭터</x:t>
   </x:si>
   <x:si>
     <x:t>skill_normalSword_01</x:t>
@@ -914,84 +920,93 @@
     <x:col min="4" max="4" width="40.22265625" style="3" customWidth="1"/>
     <x:col min="5" max="5" width="30.54296875" style="3" customWidth="1"/>
     <x:col min="6" max="6" width="26.54296875" style="3" customWidth="1"/>
-    <x:col min="7" max="16384" width="12.54296875" style="3"/>
+    <x:col min="7" max="7" width="12.54296875" style="3" bestFit="1" customWidth="1"/>
+    <x:col min="8" max="16384" width="12.54296875" style="3"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="D1" s="2" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E1" s="2" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="D1" s="2" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E1" s="2" t="s">
+    </x:row>
+    <x:row r="2" spans="1:7" ht="13.199999999999999">
+      <x:c r="A2" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B2" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C2" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D2" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E2" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F2" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G2" s="3" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:7" s="13" customFormat="1" ht="15.75" customHeight="1">
+      <x:c r="A3" s="12" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B3" s="12" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D3" s="14" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E3" s="14" t="s">
         <x:v>9</x:v>
       </x:c>
-    </x:row>
-    <x:row r="2" spans="1:6" ht="13.199999999999999">
-      <x:c r="A2" s="1" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B2" s="1" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D2" s="1" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="E2" s="1" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F2" s="1" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:6" s="13" customFormat="1" ht="15.75" customHeight="1">
-      <x:c r="A3" s="12" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B3" s="12" t="s">
+      <x:c r="F3" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="G3" s="13" t="s">
         <x:v>6</x:v>
-      </x:c>
-      <x:c r="C3" s="12" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D3" s="14" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="E3" s="14" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="F3" s="15" t="s">
-        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A4" s="4" t="s">
-        <x:v>11</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B4" s="4" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C4" s="4" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D4" s="5" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="D4" s="5" t="s">
-        <x:v>18</x:v>
-      </x:c>
       <x:c r="E4" s="5" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F4" s="16" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="G4" s="5"/>
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G4" s="5">
+        <x:v>100</x:v>
+      </x:c>
       <x:c r="H4" s="5"/>
       <x:c r="I4" s="5"/>
       <x:c r="J4" s="5"/>
@@ -1003,19 +1018,19 @@
     </x:row>
     <x:row r="5" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A5" s="4" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B5" s="6" t="s">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C5" s="6" t="s">
-        <x:v>10</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D5" s="5" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E5" s="5" t="s">
         <x:v>26</x:v>
-      </x:c>
-      <x:c r="E5" s="5" t="s">
-        <x:v>15</x:v>
       </x:c>
       <x:c r="F5" s="5"/>
       <x:c r="G5" s="5"/>
@@ -1030,19 +1045,19 @@
     </x:row>
     <x:row r="6" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A6" s="6" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B6" s="6" t="s">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C6" s="6" t="s">
-        <x:v>23</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D6" s="5" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E6" s="5" t="s">
-        <x:v>13</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F6" s="5"/>
       <x:c r="G6" s="5"/>

--- a/JsonConverter/ExcelFiles/Character.xlsx
+++ b/JsonConverter/ExcelFiles/Character.xlsx
@@ -19,96 +19,93 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="30">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="29">
+  <x:si>
+    <x:t>skill_normalSword_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_rest_coffee_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>퐁당퐁당 왕국의 공주로써 백성들을 위해&lt;nl&gt;식량을 구하러 모험을 떠나는 캐릭터</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
   <x:si>
     <x:t>셀리</x:t>
   </x:si>
   <x:si>
+    <x:t>다니엘</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스킬</x:t>
+  </x:si>
+  <x:si>
     <x:t>빅토르</x:t>
   </x:si>
   <x:si>
-    <x:t>스킬</x:t>
-  </x:si>
-  <x:si>
-    <x:t>다니엘</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
     <x:t>Hp</x:t>
   </x:si>
   <x:si>
-    <x:t>퐁당퐁당 왕국의 공주로써 백성들을 위해&lt;nl&gt;식량을 구하러 모험을 떠나는 캐릭터</x:t>
+    <x:t>캐릭터 별로 무기가 고정인 경우용</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소환 마법을 사용할 수 있는 캐릭터</x:t>
+  </x:si>
+  <x:si>
+    <x:t>character_daniel_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Weapon_CoffeeCup_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>character_victor_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>character_selly_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>잉여로운 버프 캐릭터</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UseWeaponId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Costume_03</x:t>
   </x:si>
   <x:si>
     <x:t>SkillList</x:t>
   </x:si>
   <x:si>
-    <x:t>UseWeaponId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>잉여로운 버프 캐릭터</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Costume_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 별로 무기가 고정인 경우용</x:t>
-  </x:si>
-  <x:si>
-    <x:t>character_victor_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Weapon_CoffeeCup_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>character_selly_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>character_daniel_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Weapon_Braclet_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소환 마법을 사용할 수 있는 캐릭터</x:t>
+    <x:t>skill_sword_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Weapon_Sword_1</x:t>
   </x:si>
   <x:si>
     <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
   </x:si>
   <x:si>
-    <x:t>skill_sword_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Weapon_Sword_1</x:t>
-  </x:si>
-  <x:si>
     <x:t>BasicCostumeId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_normalSword_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_rest_coffee_01</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -926,83 +923,83 @@
   <x:sheetData>
     <x:row r="1" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D1" s="2" t="s">
-        <x:v>2</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E1" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:7" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G2" s="3" t="s">
-        <x:v>5</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:7" s="13" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="12" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B3" s="12" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B3" s="12" t="s">
-        <x:v>15</x:v>
-      </x:c>
       <x:c r="C3" s="12" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D3" s="14" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E3" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F3" s="15" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="G3" s="13" t="s">
         <x:v>12</x:v>
-      </x:c>
-      <x:c r="D3" s="14" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="E3" s="14" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="F3" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="G3" s="13" t="s">
-        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A4" s="4" t="s">
-        <x:v>20</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B4" s="4" t="s">
-        <x:v>0</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C4" s="4" t="s">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D4" s="5" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="E4" s="5" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F4" s="16" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G4" s="5">
         <x:v>100</x:v>
@@ -1018,16 +1015,16 @@
     </x:row>
     <x:row r="5" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A5" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B5" s="6" t="s">
-        <x:v>1</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C5" s="6" t="s">
-        <x:v>23</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D5" s="5" t="s">
-        <x:v>28</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E5" s="5" t="s">
         <x:v>26</x:v>
@@ -1045,19 +1042,19 @@
     </x:row>
     <x:row r="6" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A6" s="6" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B6" s="6" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C6" s="6" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="B6" s="6" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C6" s="6" t="s">
-        <x:v>10</x:v>
-      </x:c>
       <x:c r="D6" s="5" t="s">
-        <x:v>29</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E6" s="5" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F6" s="5"/>
       <x:c r="G6" s="5"/>
